--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/30.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/30.xlsx
@@ -426,13 +426,13 @@
         <v>-4.908730184712091</v>
       </c>
       <c r="E2">
-        <v>-11.77707310270968</v>
+        <v>-12.26997032760055</v>
       </c>
       <c r="F2">
-        <v>-2.648420787679767</v>
+        <v>-1.963561410476053</v>
       </c>
       <c r="G2">
-        <v>-6.255336080450119</v>
+        <v>-5.98563935559312</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.876391581445067</v>
       </c>
       <c r="E3">
-        <v>-13.40069405952378</v>
+        <v>-13.25369073628678</v>
       </c>
       <c r="F3">
-        <v>-2.509005725421207</v>
+        <v>-2.15022157918588</v>
       </c>
       <c r="G3">
-        <v>-6.181905623171306</v>
+        <v>-6.101938972546079</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.94575290013681</v>
       </c>
       <c r="E4">
-        <v>-13.14403826666505</v>
+        <v>-13.1979678636224</v>
       </c>
       <c r="F4">
-        <v>-2.264025178084684</v>
+        <v>-1.528320609697137</v>
       </c>
       <c r="G4">
-        <v>-5.95065825254788</v>
+        <v>-5.852897537405784</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.094680446191441</v>
       </c>
       <c r="E5">
-        <v>-13.42266621540899</v>
+        <v>-14.22066031961864</v>
       </c>
       <c r="F5">
-        <v>-2.405058041880911</v>
+        <v>-1.531657273595613</v>
       </c>
       <c r="G5">
-        <v>-5.888173950391375</v>
+        <v>-5.443453586332035</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.279923563228212</v>
       </c>
       <c r="E6">
-        <v>-13.57753549799731</v>
+        <v>-13.42471308566046</v>
       </c>
       <c r="F6">
-        <v>-2.327741541973217</v>
+        <v>-1.650338299762101</v>
       </c>
       <c r="G6">
-        <v>-5.882061034626129</v>
+        <v>-5.75424104877796</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.450493516533032</v>
       </c>
       <c r="E7">
-        <v>-13.92559853870086</v>
+        <v>-14.14925534146569</v>
       </c>
       <c r="F7">
-        <v>-2.349891257956672</v>
+        <v>-1.449546183160515</v>
       </c>
       <c r="G7">
-        <v>-5.522009311686701</v>
+        <v>-6.006301207752943</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.556322090245139</v>
       </c>
       <c r="E8">
-        <v>-14.14437364648543</v>
+        <v>-15.82543829608682</v>
       </c>
       <c r="F8">
-        <v>-2.234681091207914</v>
+        <v>-1.324053491840807</v>
       </c>
       <c r="G8">
-        <v>-5.305839154128924</v>
+        <v>-5.045726877447063</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.55210178582319</v>
       </c>
       <c r="E9">
-        <v>-15.06076470362562</v>
+        <v>-14.42984411945496</v>
       </c>
       <c r="F9">
-        <v>-2.129728598008023</v>
+        <v>-1.424522032289345</v>
       </c>
       <c r="G9">
-        <v>-4.881957828193618</v>
+        <v>-5.396902896068193</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.410832665941475</v>
       </c>
       <c r="E10">
-        <v>-15.42657483396523</v>
+        <v>-16.20070840862846</v>
       </c>
       <c r="F10">
-        <v>-2.004520036707475</v>
+        <v>-1.476357122519524</v>
       </c>
       <c r="G10">
-        <v>-5.43662536426683</v>
+        <v>-5.077105199220032</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.117019160332051</v>
       </c>
       <c r="E11">
-        <v>-16.03223106164709</v>
+        <v>-17.45498702537697</v>
       </c>
       <c r="F11">
-        <v>-1.971163338131544</v>
+        <v>-1.022185641484431</v>
       </c>
       <c r="G11">
-        <v>-4.916476278998976</v>
+        <v>-4.568200860236395</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.678934904432954</v>
       </c>
       <c r="E12">
-        <v>-16.36165037486106</v>
+        <v>-16.22086011796259</v>
       </c>
       <c r="F12">
-        <v>-1.667428347649258</v>
+        <v>-1.534467095825909</v>
       </c>
       <c r="G12">
-        <v>-4.827328770450422</v>
+        <v>-5.097537365870695</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.113103691691698</v>
       </c>
       <c r="E13">
-        <v>-17.03098147556478</v>
+        <v>-16.89552123257334</v>
       </c>
       <c r="F13">
-        <v>-1.352246148027685</v>
+        <v>-1.417032762600634</v>
       </c>
       <c r="G13">
-        <v>-4.486501724627781</v>
+        <v>-3.740027101075667</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.458028037082135</v>
       </c>
       <c r="E14">
-        <v>-18.83100460887367</v>
+        <v>-18.39382119969917</v>
       </c>
       <c r="F14">
-        <v>-1.464879263786334</v>
+        <v>-0.8736005520768804</v>
       </c>
       <c r="G14">
-        <v>-4.669364202135635</v>
+        <v>-4.423912423381373</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.756169126461922</v>
       </c>
       <c r="E15">
-        <v>-19.46767182656006</v>
+        <v>-19.31899749641424</v>
       </c>
       <c r="F15">
-        <v>-1.210522425817523</v>
+        <v>-0.02767921564465043</v>
       </c>
       <c r="G15">
-        <v>-4.526680282623182</v>
+        <v>-4.043782905719703</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.058532587318525</v>
       </c>
       <c r="E16">
-        <v>-19.65103879607865</v>
+        <v>-19.77696660128395</v>
       </c>
       <c r="F16">
-        <v>-0.9646008531114201</v>
+        <v>-0.1401358891465029</v>
       </c>
       <c r="G16">
-        <v>-3.977987851009717</v>
+        <v>-3.564015814183934</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.407194334648513</v>
       </c>
       <c r="E17">
-        <v>-21.16774248157165</v>
+        <v>-20.95869000748156</v>
       </c>
       <c r="F17">
-        <v>-0.4669011501614211</v>
+        <v>0.650896994808829</v>
       </c>
       <c r="G17">
-        <v>-4.200553109386852</v>
+        <v>-2.179356722206061</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.834495816941599</v>
       </c>
       <c r="E18">
-        <v>-20.83091458488113</v>
+        <v>-21.43937846644775</v>
       </c>
       <c r="F18">
-        <v>0.03841870452693052</v>
+        <v>0.9072551684228032</v>
       </c>
       <c r="G18">
-        <v>-3.313720952407932</v>
+        <v>-2.554840030139558</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3581279312099459</v>
       </c>
       <c r="E19">
-        <v>-21.32489411505984</v>
+        <v>-21.00145238753599</v>
       </c>
       <c r="F19">
-        <v>0.1806966045295652</v>
+        <v>0.6449294360390614</v>
       </c>
       <c r="G19">
-        <v>-3.989475407689333</v>
+        <v>-2.28165208554331</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.01984359498274018</v>
       </c>
       <c r="E20">
-        <v>-22.11373164482598</v>
+        <v>-20.05194912845171</v>
       </c>
       <c r="F20">
-        <v>0.6679514228976652</v>
+        <v>0.927356331819136</v>
       </c>
       <c r="G20">
-        <v>-3.684462895188031</v>
+        <v>-1.761919715413504</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.3047895575438113</v>
       </c>
       <c r="E21">
-        <v>-22.25557703616823</v>
+        <v>-23.82689864666775</v>
       </c>
       <c r="F21">
-        <v>0.8735290179852241</v>
+        <v>0.7897992976450556</v>
       </c>
       <c r="G21">
-        <v>-3.191108265174602</v>
+        <v>-2.793722803331812</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.5124760605191488</v>
       </c>
       <c r="E22">
-        <v>-22.76255328674895</v>
+        <v>-23.85321360912632</v>
       </c>
       <c r="F22">
-        <v>0.843459281263602</v>
+        <v>1.723092685887563</v>
       </c>
       <c r="G22">
-        <v>-3.566745790521392</v>
+        <v>-3.217282569554292</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.6557655808559893</v>
       </c>
       <c r="E23">
-        <v>-23.2566731996219</v>
+        <v>-24.25235783663639</v>
       </c>
       <c r="F23">
-        <v>1.072966753883233</v>
+        <v>1.229813151398903</v>
       </c>
       <c r="G23">
-        <v>-4.122912844847272</v>
+        <v>-3.026272818914337</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.7528645296964181</v>
       </c>
       <c r="E24">
-        <v>-24.38504212506113</v>
+        <v>-23.30596111072138</v>
       </c>
       <c r="F24">
-        <v>1.228008967195605</v>
+        <v>2.191572557071213</v>
       </c>
       <c r="G24">
-        <v>-3.504921013898335</v>
+        <v>-3.077108784534814</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.8139984763606549</v>
       </c>
       <c r="E25">
-        <v>-24.08834556502659</v>
+        <v>-25.19077086287588</v>
       </c>
       <c r="F25">
-        <v>1.597076466369286</v>
+        <v>1.449623755201363</v>
       </c>
       <c r="G25">
-        <v>-4.179602509729798</v>
+        <v>-1.522607102196964</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.8517272143068525</v>
       </c>
       <c r="E26">
-        <v>-23.2820598249089</v>
+        <v>-24.42573499249406</v>
       </c>
       <c r="F26">
-        <v>1.410503276236753</v>
+        <v>1.749060347230522</v>
       </c>
       <c r="G26">
-        <v>-3.510817369040657</v>
+        <v>-4.05455515609936</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.8702337879947659</v>
       </c>
       <c r="E27">
-        <v>-24.55203866104199</v>
+        <v>-24.45872039716593</v>
       </c>
       <c r="F27">
-        <v>1.352708082543432</v>
+        <v>1.926887634324298</v>
       </c>
       <c r="G27">
-        <v>-3.969597767482217</v>
+        <v>-2.633047946008923</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.874727395886325</v>
       </c>
       <c r="E28">
-        <v>-24.30683085047466</v>
+        <v>-24.64155300675161</v>
       </c>
       <c r="F28">
-        <v>1.085503266157201</v>
+        <v>1.711944517380688</v>
       </c>
       <c r="G28">
-        <v>-3.916320573021513</v>
+        <v>-2.9076008787739</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.8669006730523237</v>
       </c>
       <c r="E29">
-        <v>-22.51854099331964</v>
+        <v>-22.80387561206895</v>
       </c>
       <c r="F29">
-        <v>1.031523532721174</v>
+        <v>1.67631312191667</v>
       </c>
       <c r="G29">
-        <v>-3.996129725011887</v>
+        <v>-3.130061138061133</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.8497483073862795</v>
       </c>
       <c r="E30">
-        <v>-23.30678076451677</v>
+        <v>-24.34916302549836</v>
       </c>
       <c r="F30">
-        <v>1.352005626985858</v>
+        <v>2.283209872638505</v>
       </c>
       <c r="G30">
-        <v>-3.408584348913038</v>
+        <v>-1.70108258647984</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.8262308472062851</v>
       </c>
       <c r="E31">
-        <v>-22.34328452074879</v>
+        <v>-23.5387020323456</v>
       </c>
       <c r="F31">
-        <v>1.017754409751841</v>
+        <v>1.506257577795959</v>
       </c>
       <c r="G31">
-        <v>-3.089144305214857</v>
+        <v>-2.507065444234043</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.7995867983411477</v>
       </c>
       <c r="E32">
-        <v>-22.78218422157221</v>
+        <v>-23.80748960707087</v>
       </c>
       <c r="F32">
-        <v>1.062865641773496</v>
+        <v>1.065486596235954</v>
       </c>
       <c r="G32">
-        <v>-3.276941739948116</v>
+        <v>-4.704407648390505</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7733212178999121</v>
       </c>
       <c r="E33">
-        <v>-21.94099300380339</v>
+        <v>-22.48349060450028</v>
       </c>
       <c r="F33">
-        <v>0.5198989737301152</v>
+        <v>1.187148916685117</v>
       </c>
       <c r="G33">
-        <v>-2.899122202264294</v>
+        <v>-1.537277443789241</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.7514196327102228</v>
       </c>
       <c r="E34">
-        <v>-21.61896416016993</v>
+        <v>-22.05402824350885</v>
       </c>
       <c r="F34">
-        <v>0.3756404472673869</v>
+        <v>1.658370683972032</v>
       </c>
       <c r="G34">
-        <v>-3.15182219944337</v>
+        <v>-3.320394957059842</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.73995172903267</v>
       </c>
       <c r="E35">
-        <v>-21.03878059878122</v>
+        <v>-22.64109055691522</v>
       </c>
       <c r="F35">
-        <v>0.5660299260246169</v>
+        <v>1.565248934018923</v>
       </c>
       <c r="G35">
-        <v>-3.424773896087338</v>
+        <v>-3.670081301092984</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.7437845462067204</v>
       </c>
       <c r="E36">
-        <v>-20.65040961093539</v>
+        <v>-19.74603712381156</v>
       </c>
       <c r="F36">
-        <v>0.9844325026068275</v>
+        <v>1.990236203085987</v>
       </c>
       <c r="G36">
-        <v>-2.926759931459498</v>
+        <v>-2.128668411555759</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.7664328093201177</v>
       </c>
       <c r="E37">
-        <v>-20.41289114923308</v>
+        <v>-21.46419450400979</v>
       </c>
       <c r="F37">
-        <v>0.600536398555633</v>
+        <v>1.835076361602417</v>
       </c>
       <c r="G37">
-        <v>-3.174085287724203</v>
+        <v>-3.443598264173872</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.8068409444448265</v>
       </c>
       <c r="E38">
-        <v>-20.77570342977961</v>
+        <v>-21.98419464583656</v>
       </c>
       <c r="F38">
-        <v>0.4881882411835473</v>
+        <v>0.8272265936383429</v>
       </c>
       <c r="G38">
-        <v>-2.919272183860845</v>
+        <v>-1.852570023436284</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.8611833702802494</v>
       </c>
       <c r="E39">
-        <v>-19.65996441834777</v>
+        <v>-21.22126904434232</v>
       </c>
       <c r="F39">
-        <v>0.6266597929703183</v>
+        <v>1.527248407782899</v>
       </c>
       <c r="G39">
-        <v>-2.72648401113567</v>
+        <v>-2.567620388113595</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.9224343263401688</v>
       </c>
       <c r="E40">
-        <v>-18.75863506575709</v>
+        <v>-21.61346206425062</v>
       </c>
       <c r="F40">
-        <v>0.6417393931708805</v>
+        <v>1.312855326794748</v>
       </c>
       <c r="G40">
-        <v>-2.706271686329491</v>
+        <v>-1.627301038494166</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.9829486677787943</v>
       </c>
       <c r="E41">
-        <v>-18.29183996504643</v>
+        <v>-19.07251265617674</v>
       </c>
       <c r="F41">
-        <v>0.4302331725814855</v>
+        <v>1.469642081857416</v>
       </c>
       <c r="G41">
-        <v>-2.453099193245856</v>
+        <v>-1.895662306176471</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.036590576061075</v>
       </c>
       <c r="E42">
-        <v>-18.36030143509439</v>
+        <v>-19.11956350111643</v>
       </c>
       <c r="F42">
-        <v>0.1331242929541924</v>
+        <v>0.560063195622252</v>
       </c>
       <c r="G42">
-        <v>-3.062782971206278</v>
+        <v>-2.149477918685758</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.080237239147192</v>
       </c>
       <c r="E43">
-        <v>-17.94953714328064</v>
+        <v>-19.30731403347445</v>
       </c>
       <c r="F43">
-        <v>0.6100510265441882</v>
+        <v>0.824156664043568</v>
       </c>
       <c r="G43">
-        <v>-3.253986313918241</v>
+        <v>-2.383215736472802</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.114083032840717</v>
       </c>
       <c r="E44">
-        <v>-18.43919650925602</v>
+        <v>-18.56845274285696</v>
       </c>
       <c r="F44">
-        <v>0.0882168393136256</v>
+        <v>0.847157113349699</v>
       </c>
       <c r="G44">
-        <v>-2.809945162721706</v>
+        <v>-1.598006292411444</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.140515181773889</v>
       </c>
       <c r="E45">
-        <v>-16.49192098663972</v>
+        <v>-18.24821264645653</v>
       </c>
       <c r="F45">
-        <v>0.4300857231837872</v>
+        <v>1.079227554713592</v>
       </c>
       <c r="G45">
-        <v>-2.939868411589479</v>
+        <v>-1.546681424778609</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.163842706019623</v>
       </c>
       <c r="E46">
-        <v>-16.56976998330558</v>
+        <v>-15.35817223407937</v>
       </c>
       <c r="F46">
-        <v>0.5055118886782933</v>
+        <v>0.7265352223584518</v>
       </c>
       <c r="G46">
-        <v>-3.339813226248636</v>
+        <v>-1.462226063060062</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.188492622778699</v>
       </c>
       <c r="E47">
-        <v>-16.01176235913242</v>
+        <v>-17.5942194872168</v>
       </c>
       <c r="F47">
-        <v>0.2995234233589459</v>
+        <v>0.6469738467891705</v>
       </c>
       <c r="G47">
-        <v>-2.633044664787363</v>
+        <v>-2.097733054693315</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.218186067428611</v>
       </c>
       <c r="E48">
-        <v>-15.82817349438746</v>
+        <v>-15.92474773107504</v>
       </c>
       <c r="F48">
-        <v>0.1822183154485079</v>
+        <v>0.876991593728926</v>
       </c>
       <c r="G48">
-        <v>-2.888550106399764</v>
+        <v>-1.940533011001877</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.253737956260878</v>
       </c>
       <c r="E49">
-        <v>-15.07948994364733</v>
+        <v>-16.66864015631505</v>
       </c>
       <c r="F49">
-        <v>-0.06053806541149842</v>
+        <v>0.3424303697217519</v>
       </c>
       <c r="G49">
-        <v>-2.648830621709852</v>
+        <v>-1.638690158526999</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.295009788187494</v>
       </c>
       <c r="E50">
-        <v>-14.88785398059074</v>
+        <v>-15.3805066678852</v>
       </c>
       <c r="F50">
-        <v>-0.05252112568720481</v>
+        <v>0.4072741416454944</v>
       </c>
       <c r="G50">
-        <v>-3.285591039978812</v>
+        <v>-2.489192630399747</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.339106308068467</v>
       </c>
       <c r="E51">
-        <v>-14.46578661765384</v>
+        <v>-14.6959553660417</v>
       </c>
       <c r="F51">
-        <v>0.0265448861752024</v>
+        <v>0.05407733354204957</v>
       </c>
       <c r="G51">
-        <v>-3.061956103373298</v>
+        <v>-2.275827917275295</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.382271279905073</v>
       </c>
       <c r="E52">
-        <v>-13.885530600681</v>
+        <v>-14.11845266126552</v>
       </c>
       <c r="F52">
-        <v>0.1775645473795803</v>
+        <v>-0.02232382038555163</v>
       </c>
       <c r="G52">
-        <v>-3.571031065878027</v>
+        <v>-2.36933945049791</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.418600777369438</v>
       </c>
       <c r="E53">
-        <v>-12.25298402159778</v>
+        <v>-15.37822884545934</v>
       </c>
       <c r="F53">
-        <v>-0.1583674273147172</v>
+        <v>0.8562575576368544</v>
       </c>
       <c r="G53">
-        <v>-3.781101432556796</v>
+        <v>-2.25435232216873</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.441279639388984</v>
       </c>
       <c r="E54">
-        <v>-12.62394302688411</v>
+        <v>-14.05862699115019</v>
       </c>
       <c r="F54">
-        <v>-0.1474893065811541</v>
+        <v>-0.4927578102724048</v>
       </c>
       <c r="G54">
-        <v>-2.733669886350854</v>
+        <v>-2.09392027524124</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.444095157945109</v>
       </c>
       <c r="E55">
-        <v>-11.87094836888869</v>
+        <v>-13.12015962322261</v>
       </c>
       <c r="F55">
-        <v>0.1279271158690283</v>
+        <v>0.3315315398031188</v>
       </c>
       <c r="G55">
-        <v>-3.594436019261546</v>
+        <v>-2.988761894046765</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.420158163891594</v>
       </c>
       <c r="E56">
-        <v>-12.02278357389186</v>
+        <v>-11.97523459681133</v>
       </c>
       <c r="F56">
-        <v>-0.1426458423769854</v>
+        <v>0.3641095730204177</v>
       </c>
       <c r="G56">
-        <v>-3.719555559766292</v>
+        <v>-4.119746466042407</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.366518242796602</v>
       </c>
       <c r="E57">
-        <v>-11.18284674342317</v>
+        <v>-12.42924581539833</v>
       </c>
       <c r="F57">
-        <v>-0.2937027801144892</v>
+        <v>0.6141738111079212</v>
       </c>
       <c r="G57">
-        <v>-3.904186615694687</v>
+        <v>-1.464752603660834</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.282405473451299</v>
       </c>
       <c r="E58">
-        <v>-12.10886533630367</v>
+        <v>-11.48929763647024</v>
       </c>
       <c r="F58">
-        <v>-0.2049167051476327</v>
+        <v>0.002778197021481789</v>
       </c>
       <c r="G58">
-        <v>-4.662634416717213</v>
+        <v>-3.048135598164917</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.171725315554065</v>
       </c>
       <c r="E59">
-        <v>-11.42928629892059</v>
+        <v>-11.70754744126991</v>
       </c>
       <c r="F59">
-        <v>-0.1193405538666241</v>
+        <v>0.002310169438900069</v>
       </c>
       <c r="G59">
-        <v>-3.902122727333796</v>
+        <v>-2.74326745941223</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.039342558947815</v>
       </c>
       <c r="E60">
-        <v>-10.62523309648869</v>
+        <v>-11.69772970962129</v>
       </c>
       <c r="F60">
-        <v>-0.7475561680669076</v>
+        <v>-0.06999139421224639</v>
       </c>
       <c r="G60">
-        <v>-3.780710967191223</v>
+        <v>-2.270689524313205</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.8916998761321284</v>
       </c>
       <c r="E61">
-        <v>-10.2892520244376</v>
+        <v>-11.40352381029096</v>
       </c>
       <c r="F61">
-        <v>-0.3506348149740937</v>
+        <v>-0.7538492752259754</v>
       </c>
       <c r="G61">
-        <v>-4.191953027679547</v>
+        <v>-2.841677856423096</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7354266612016188</v>
       </c>
       <c r="E62">
-        <v>-9.834212842250849</v>
+        <v>-10.86527844668727</v>
       </c>
       <c r="F62">
-        <v>-0.6629856548128976</v>
+        <v>0.7034544214142492</v>
       </c>
       <c r="G62">
-        <v>-4.142954546132359</v>
+        <v>-2.9279247651131</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.5775493013370269</v>
       </c>
       <c r="E63">
-        <v>-9.303357948227683</v>
+        <v>-10.94766044583481</v>
       </c>
       <c r="F63">
-        <v>-0.4063715156714584</v>
+        <v>-0.06580648209330328</v>
       </c>
       <c r="G63">
-        <v>-4.4847364274288</v>
+        <v>-2.504604528064459</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.426134730530199</v>
       </c>
       <c r="E64">
-        <v>-9.907139387670373</v>
+        <v>-12.74247583403488</v>
       </c>
       <c r="F64">
-        <v>-0.9680741976313584</v>
+        <v>-0.5378466763741847</v>
       </c>
       <c r="G64">
-        <v>-4.700437370303576</v>
+        <v>-2.928538353544716</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.2885107444239361</v>
       </c>
       <c r="E65">
-        <v>-9.327354331994329</v>
+        <v>-10.19232909525143</v>
       </c>
       <c r="F65">
-        <v>-0.7175195660413975</v>
+        <v>-0.7346899655666257</v>
       </c>
       <c r="G65">
-        <v>-4.019905456431624</v>
+        <v>-3.963711256004573</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.1714097506169827</v>
       </c>
       <c r="E66">
-        <v>-9.163654525091054</v>
+        <v>-9.312351497606917</v>
       </c>
       <c r="F66">
-        <v>-1.00979326513855</v>
+        <v>-0.6339190710160658</v>
       </c>
       <c r="G66">
-        <v>-4.838448830315381</v>
+        <v>-3.678586227375065</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.07915756113539714</v>
       </c>
       <c r="E67">
-        <v>-8.4590556688156</v>
+        <v>-9.418974418117516</v>
       </c>
       <c r="F67">
-        <v>-1.079120989813646</v>
+        <v>-0.7026338038130904</v>
       </c>
       <c r="G67">
-        <v>-3.766851087324128</v>
+        <v>-2.846980310463159</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.01519006269732988</v>
       </c>
       <c r="E68">
-        <v>-9.164931554761216</v>
+        <v>-10.66439081123301</v>
       </c>
       <c r="F68">
-        <v>-1.134397118235054</v>
+        <v>-0.838346892148539</v>
       </c>
       <c r="G68">
-        <v>-4.870174961573651</v>
+        <v>-4.067420825833942</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.0207137299660262</v>
       </c>
       <c r="E69">
-        <v>-9.507324946007165</v>
+        <v>-10.51160462668822</v>
       </c>
       <c r="F69">
-        <v>-1.026438479730403</v>
+        <v>-1.01492417283149</v>
       </c>
       <c r="G69">
-        <v>-4.952677996464329</v>
+        <v>-4.084092712577481</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.02938965924963452</v>
       </c>
       <c r="E70">
-        <v>-9.714217337995601</v>
+        <v>-10.11734209415842</v>
       </c>
       <c r="F70">
-        <v>-1.371061685214873</v>
+        <v>-1.285328144127333</v>
       </c>
       <c r="G70">
-        <v>-4.087341121921331</v>
+        <v>-2.92449588858348</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.01430116265039691</v>
       </c>
       <c r="E71">
-        <v>-9.303303606539592</v>
+        <v>-10.30193628013308</v>
       </c>
       <c r="F71">
-        <v>-1.596904460444519</v>
+        <v>-0.9379125121280256</v>
       </c>
       <c r="G71">
-        <v>-4.186237139722995</v>
+        <v>-4.432463286765286</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.02169566547203771</v>
       </c>
       <c r="E72">
-        <v>-9.904920435406614</v>
+        <v>-10.22652360248335</v>
       </c>
       <c r="F72">
-        <v>-1.327547545545815</v>
+        <v>-1.494830543969356</v>
       </c>
       <c r="G72">
-        <v>-3.760600360253386</v>
+        <v>-4.378172194842714</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.07425679429340275</v>
       </c>
       <c r="E73">
-        <v>-9.78273767820566</v>
+        <v>-10.33204610381008</v>
       </c>
       <c r="F73">
-        <v>-1.930670254380496</v>
+        <v>-1.322190493551911</v>
       </c>
       <c r="G73">
-        <v>-3.552708724690087</v>
+        <v>-3.919874135970392</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.1393288265567108</v>
       </c>
       <c r="E74">
-        <v>-11.00812915925924</v>
+        <v>-11.1022761338787</v>
       </c>
       <c r="F74">
-        <v>-2.124556271944943</v>
+        <v>-1.583261249320411</v>
       </c>
       <c r="G74">
-        <v>-3.445307780606343</v>
+        <v>-3.426132321812948</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2121940906314063</v>
       </c>
       <c r="E75">
-        <v>-10.52322921946591</v>
+        <v>-10.61417909143596</v>
       </c>
       <c r="F75">
-        <v>-2.080066315475387</v>
+        <v>-1.234031492708973</v>
       </c>
       <c r="G75">
-        <v>-3.389149673616447</v>
+        <v>-2.493563217516928</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.2880946666831988</v>
       </c>
       <c r="E76">
-        <v>-11.05160703820688</v>
+        <v>-11.09788804256527</v>
       </c>
       <c r="F76">
-        <v>-1.832465642043809</v>
+        <v>-1.206381417170929</v>
       </c>
       <c r="G76">
-        <v>-2.929565375892823</v>
+        <v>-2.55754375670454</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3617926184473396</v>
       </c>
       <c r="E77">
-        <v>-10.84820157120435</v>
+        <v>-12.10881099461558</v>
       </c>
       <c r="F77">
-        <v>-2.187518821496927</v>
+        <v>-2.181347484346071</v>
       </c>
       <c r="G77">
-        <v>-3.794725064471611</v>
+        <v>-2.441601792901561</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.4282091951525928</v>
       </c>
       <c r="E78">
-        <v>-11.36680694303677</v>
+        <v>-13.15967508741354</v>
       </c>
       <c r="F78">
-        <v>-1.988635263391391</v>
+        <v>-1.842358005568041</v>
       </c>
       <c r="G78">
-        <v>-2.854103842468713</v>
+        <v>-2.641949900099696</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.4832425004168192</v>
       </c>
       <c r="E79">
-        <v>-11.7310366359477</v>
+        <v>-13.87125685060882</v>
       </c>
       <c r="F79">
-        <v>-1.974555502646008</v>
+        <v>-1.323617770586934</v>
       </c>
       <c r="G79">
-        <v>-2.373293322477041</v>
+        <v>-4.447848934657523</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5224408622592384</v>
       </c>
       <c r="E80">
-        <v>-11.88969172280643</v>
+        <v>-12.43720687270382</v>
       </c>
       <c r="F80">
-        <v>-2.227626714405674</v>
+        <v>-1.83244824632835</v>
       </c>
       <c r="G80">
-        <v>-2.479122561433812</v>
+        <v>-2.565238221261438</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.5417271634930133</v>
       </c>
       <c r="E81">
-        <v>-12.39500602342634</v>
+        <v>-13.0067439917005</v>
       </c>
       <c r="F81">
-        <v>-1.998918616329744</v>
+        <v>-2.383706043706351</v>
       </c>
       <c r="G81">
-        <v>-1.710260163181607</v>
+        <v>-2.106530009694186</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.5352667603245302</v>
       </c>
       <c r="E82">
-        <v>-14.75556366940466</v>
+        <v>-14.92043635107593</v>
       </c>
       <c r="F82">
-        <v>-2.305567803335079</v>
+        <v>-2.325489211005005</v>
       </c>
       <c r="G82">
-        <v>-2.264310829601644</v>
+        <v>-2.616917460822692</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.4987924192545604</v>
       </c>
       <c r="E83">
-        <v>-14.03794997883116</v>
+        <v>-14.955310129409</v>
       </c>
       <c r="F83">
-        <v>-2.588312792197829</v>
+        <v>-2.159561421652444</v>
       </c>
       <c r="G83">
-        <v>-1.679013090271015</v>
+        <v>-2.974685453556747</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.4263194051908865</v>
       </c>
       <c r="E84">
-        <v>-15.91589003591603</v>
+        <v>-16.30229566604253</v>
       </c>
       <c r="F84">
-        <v>-2.75217546161521</v>
+        <v>-1.641528612433328</v>
       </c>
       <c r="G84">
-        <v>-2.766298353537973</v>
+        <v>-1.796877849907828</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3141225996638258</v>
       </c>
       <c r="E85">
-        <v>-15.95428696702707</v>
+        <v>-17.36744709433469</v>
       </c>
       <c r="F85">
-        <v>-2.549375382429238</v>
+        <v>-2.069272688216909</v>
       </c>
       <c r="G85">
-        <v>-1.604982169446823</v>
+        <v>-2.08097585618923</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.1574564712698162</v>
       </c>
       <c r="E86">
-        <v>-17.27790104930702</v>
+        <v>-18.44205850482887</v>
       </c>
       <c r="F86">
-        <v>-2.950677142348056</v>
+        <v>-2.537846993284477</v>
       </c>
       <c r="G86">
-        <v>-1.5090359698271</v>
+        <v>-1.242430155679098</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.04431668626306788</v>
       </c>
       <c r="E87">
-        <v>-18.39660168273988</v>
+        <v>-20.78175799952787</v>
       </c>
       <c r="F87">
-        <v>-2.916681772504567</v>
+        <v>-2.421346230122158</v>
       </c>
       <c r="G87">
-        <v>-1.308727237287679</v>
+        <v>-3.267577133617461</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2900614289994413</v>
       </c>
       <c r="E88">
-        <v>-20.09402318045698</v>
+        <v>-19.97668136197023</v>
       </c>
       <c r="F88">
-        <v>-2.899617404006897</v>
+        <v>-2.677642276180922</v>
       </c>
       <c r="G88">
-        <v>-1.205050479673904</v>
+        <v>-2.307642641515671</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5757767504876711</v>
       </c>
       <c r="E89">
-        <v>-21.38956072388937</v>
+        <v>-23.73222636906339</v>
       </c>
       <c r="F89">
-        <v>-3.372756841831293</v>
+        <v>-2.552577850808461</v>
       </c>
       <c r="G89">
-        <v>-1.239601742694857</v>
+        <v>-2.097309777112146</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.8948646278911779</v>
       </c>
       <c r="E90">
-        <v>-22.7427412129654</v>
+        <v>-25.80062951443686</v>
       </c>
       <c r="F90">
-        <v>-3.292439995190659</v>
+        <v>-1.984147997170426</v>
       </c>
       <c r="G90">
-        <v>-1.374555104213258</v>
+        <v>-1.911609042955372</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.240474531137664</v>
       </c>
       <c r="E91">
-        <v>-24.48868530967469</v>
+        <v>-24.49538745120604</v>
       </c>
       <c r="F91">
-        <v>-3.243748559254104</v>
+        <v>-3.085169217131778</v>
       </c>
       <c r="G91">
-        <v>-0.9297034912915412</v>
+        <v>-0.1120919843306664</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.601819022533049</v>
       </c>
       <c r="E92">
-        <v>-26.34894620423361</v>
+        <v>-28.0133596549088</v>
       </c>
       <c r="F92">
-        <v>-3.777688507709179</v>
+        <v>-2.782271706093722</v>
       </c>
       <c r="G92">
-        <v>-1.610455247007977</v>
+        <v>-2.605577559113252</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.972336179808584</v>
       </c>
       <c r="E93">
-        <v>-28.11679905819201</v>
+        <v>-28.93071980548663</v>
       </c>
       <c r="F93">
-        <v>-3.821513285154287</v>
+        <v>-3.511449567714612</v>
       </c>
       <c r="G93">
-        <v>-1.52422146320421</v>
+        <v>-2.178880945079942</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.338940588594684</v>
       </c>
       <c r="E94">
-        <v>-29.93356848838126</v>
+        <v>-31.43100578120863</v>
       </c>
       <c r="F94">
-        <v>-4.164408516236517</v>
+        <v>-3.534355583136824</v>
       </c>
       <c r="G94">
-        <v>-1.898782747879503</v>
+        <v>-1.648711009169543</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.695552683797888</v>
       </c>
       <c r="E95">
-        <v>-32.28240870786475</v>
+        <v>-33.76653228710956</v>
       </c>
       <c r="F95">
-        <v>-3.644163966051926</v>
+        <v>-3.342921533084664</v>
       </c>
       <c r="G95">
-        <v>-1.958924257842565</v>
+        <v>-2.74976755932149</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.031174617607034</v>
       </c>
       <c r="E96">
-        <v>-34.09618255249792</v>
+        <v>-34.32558146030448</v>
       </c>
       <c r="F96">
-        <v>-4.047341149770682</v>
+        <v>-3.485151387777936</v>
       </c>
       <c r="G96">
-        <v>-1.758661462404976</v>
+        <v>-2.451767017292721</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.341873551507501</v>
       </c>
       <c r="E97">
-        <v>-36.90609388154637</v>
+        <v>-38.33303641949633</v>
       </c>
       <c r="F97">
-        <v>-4.192316214036832</v>
+        <v>-4.266916497230747</v>
       </c>
       <c r="G97">
-        <v>-2.426032396601996</v>
+        <v>-2.210400359379967</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.622856732426185</v>
       </c>
       <c r="E98">
-        <v>-39.30636171609796</v>
+        <v>-38.24677351812422</v>
       </c>
       <c r="F98">
-        <v>-4.542295643147804</v>
+        <v>-4.254321999238583</v>
       </c>
       <c r="G98">
-        <v>-2.697970195784096</v>
+        <v>-1.005657207949568</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.870741387383895</v>
       </c>
       <c r="E99">
-        <v>-41.62095308666143</v>
+        <v>-44.28358938403242</v>
       </c>
       <c r="F99">
-        <v>-4.696166544952617</v>
+        <v>-3.944691517950573</v>
       </c>
       <c r="G99">
-        <v>-2.925201351218761</v>
+        <v>-2.706760588341848</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.083606206564347</v>
       </c>
       <c r="E100">
-        <v>-44.4529022344682</v>
+        <v>-45.31485197708817</v>
       </c>
       <c r="F100">
-        <v>-4.874474285140017</v>
+        <v>-3.781886673706567</v>
       </c>
       <c r="G100">
-        <v>-3.024724082338279</v>
+        <v>-2.225766319942847</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.250516252943399</v>
       </c>
       <c r="E101">
-        <v>-46.59903210770933</v>
+        <v>-46.44591081608797</v>
       </c>
       <c r="F101">
-        <v>-5.164587602050668</v>
+        <v>-4.828864375941876</v>
       </c>
       <c r="G101">
-        <v>-3.071015556098925</v>
+        <v>-3.519561824496577</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.374764711721083</v>
       </c>
       <c r="E102">
-        <v>-49.7955426591481</v>
+        <v>-48.68377285518397</v>
       </c>
       <c r="F102">
-        <v>-5.152606095936576</v>
+        <v>-4.731522922438906</v>
       </c>
       <c r="G102">
-        <v>-3.943649867390128</v>
+        <v>-2.543112944286102</v>
       </c>
     </row>
   </sheetData>
